--- a/public/assets/templates/Template_Rapbs_Kegiatan.xlsx
+++ b/public/assets/templates/Template_Rapbs_Kegiatan.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_KULIAH\semester2\PBL\Template_Import_SIA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D51560E-1C82-488A-A4A3-01D7995F1DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{502B1C6E-2088-431E-B81C-00B2D87E1760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{AC1335BE-EAD5-46A9-BDC0-ECAA1E103BF0}"/>
   </bookViews>
@@ -1701,7 +1701,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1718,6 +1722,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1761,22 +1772,24 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Comma" xfId="2" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{6D3851EE-4553-4B90-8CC1-6308A2F13413}"/>
   </cellStyles>
@@ -2120,10 +2133,10 @@
       <c r="B2" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="C2" s="3">
-        <v>0</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="4">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2134,10 +2147,10 @@
       <c r="B3" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="C3" s="3">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="C3" s="4">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2148,10 +2161,10 @@
       <c r="B4" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="C4" s="3">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="C4" s="4">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2162,10 +2175,10 @@
       <c r="B5" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="C5" s="3">
-        <v>0</v>
-      </c>
-      <c r="D5" s="4" t="s">
+      <c r="C5" s="4">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2176,10 +2189,10 @@
       <c r="B6" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="C6" s="3">
-        <v>0</v>
-      </c>
-      <c r="D6" s="4" t="s">
+      <c r="C6" s="4">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2190,10 +2203,10 @@
       <c r="B7" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="C7" s="3">
-        <v>0</v>
-      </c>
-      <c r="D7" s="4" t="s">
+      <c r="C7" s="4">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2204,10 +2217,10 @@
       <c r="B8" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="C8" s="3">
-        <v>0</v>
-      </c>
-      <c r="D8" s="4" t="s">
+      <c r="C8" s="4">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2218,10 +2231,10 @@
       <c r="B9" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="C9" s="3">
-        <v>0</v>
-      </c>
-      <c r="D9" s="4" t="s">
+      <c r="C9" s="4">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2232,10 +2245,10 @@
       <c r="B10" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="C10" s="3">
-        <v>0</v>
-      </c>
-      <c r="D10" s="4" t="s">
+      <c r="C10" s="4">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2246,10 +2259,10 @@
       <c r="B11" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="C11" s="3">
-        <v>0</v>
-      </c>
-      <c r="D11" s="4" t="s">
+      <c r="C11" s="4">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2260,10 +2273,10 @@
       <c r="B12" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C12" s="3">
-        <v>0</v>
-      </c>
-      <c r="D12" s="4" t="s">
+      <c r="C12" s="4">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2274,10 +2287,10 @@
       <c r="B13" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="C13" s="3">
-        <v>0</v>
-      </c>
-      <c r="D13" s="4" t="s">
+      <c r="C13" s="4">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2288,10 +2301,10 @@
       <c r="B14" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="C14" s="3">
-        <v>0</v>
-      </c>
-      <c r="D14" s="4" t="s">
+      <c r="C14" s="4">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2302,10 +2315,10 @@
       <c r="B15" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="C15" s="3">
-        <v>0</v>
-      </c>
-      <c r="D15" s="4" t="s">
+      <c r="C15" s="4">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2316,10 +2329,10 @@
       <c r="B16" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="C16" s="3">
-        <v>0</v>
-      </c>
-      <c r="D16" s="4" t="s">
+      <c r="C16" s="4">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2330,10 +2343,10 @@
       <c r="B17" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="C17" s="3">
-        <v>0</v>
-      </c>
-      <c r="D17" s="4" t="s">
+      <c r="C17" s="4">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2344,10 +2357,10 @@
       <c r="B18" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="C18" s="3">
-        <v>0</v>
-      </c>
-      <c r="D18" s="4" t="s">
+      <c r="C18" s="4">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2358,10 +2371,10 @@
       <c r="B19" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="C19" s="3">
-        <v>0</v>
-      </c>
-      <c r="D19" s="4" t="s">
+      <c r="C19" s="4">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2372,10 +2385,10 @@
       <c r="B20" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="C20" s="3">
-        <v>0</v>
-      </c>
-      <c r="D20" s="4" t="s">
+      <c r="C20" s="4">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2386,10 +2399,10 @@
       <c r="B21" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="C21" s="3">
-        <v>0</v>
-      </c>
-      <c r="D21" s="4" t="s">
+      <c r="C21" s="4">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2400,10 +2413,10 @@
       <c r="B22" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="C22" s="3">
-        <v>0</v>
-      </c>
-      <c r="D22" s="4" t="s">
+      <c r="C22" s="4">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2414,10 +2427,10 @@
       <c r="B23" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="C23" s="3">
-        <v>0</v>
-      </c>
-      <c r="D23" s="4" t="s">
+      <c r="C23" s="4">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2428,10 +2441,10 @@
       <c r="B24" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="C24" s="3">
-        <v>0</v>
-      </c>
-      <c r="D24" s="4" t="s">
+      <c r="C24" s="4">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2442,10 +2455,10 @@
       <c r="B25" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="C25" s="3">
-        <v>0</v>
-      </c>
-      <c r="D25" s="4" t="s">
+      <c r="C25" s="4">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2456,10 +2469,10 @@
       <c r="B26" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="C26" s="3">
-        <v>0</v>
-      </c>
-      <c r="D26" s="4" t="s">
+      <c r="C26" s="4">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2470,10 +2483,10 @@
       <c r="B27" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="C27" s="3">
-        <v>0</v>
-      </c>
-      <c r="D27" s="4" t="s">
+      <c r="C27" s="4">
+        <v>0</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2484,10 +2497,10 @@
       <c r="B28" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="C28" s="3">
-        <v>0</v>
-      </c>
-      <c r="D28" s="4" t="s">
+      <c r="C28" s="4">
+        <v>0</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2498,10 +2511,10 @@
       <c r="B29" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="C29" s="3">
-        <v>0</v>
-      </c>
-      <c r="D29" s="4" t="s">
+      <c r="C29" s="4">
+        <v>0</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2512,10 +2525,10 @@
       <c r="B30" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="C30" s="3">
-        <v>0</v>
-      </c>
-      <c r="D30" s="4" t="s">
+      <c r="C30" s="4">
+        <v>0</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2526,10 +2539,10 @@
       <c r="B31" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="C31" s="3">
-        <v>0</v>
-      </c>
-      <c r="D31" s="4" t="s">
+      <c r="C31" s="4">
+        <v>0</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2540,10 +2553,10 @@
       <c r="B32" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="C32" s="3">
-        <v>0</v>
-      </c>
-      <c r="D32" s="4" t="s">
+      <c r="C32" s="4">
+        <v>0</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2554,10 +2567,10 @@
       <c r="B33" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="C33" s="3">
-        <v>0</v>
-      </c>
-      <c r="D33" s="4" t="s">
+      <c r="C33" s="4">
+        <v>0</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2568,10 +2581,10 @@
       <c r="B34" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="C34" s="3">
-        <v>0</v>
-      </c>
-      <c r="D34" s="4" t="s">
+      <c r="C34" s="4">
+        <v>0</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2582,10 +2595,10 @@
       <c r="B35" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="C35" s="3">
-        <v>0</v>
-      </c>
-      <c r="D35" s="4" t="s">
+      <c r="C35" s="4">
+        <v>0</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2596,10 +2609,10 @@
       <c r="B36" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="C36" s="3">
-        <v>0</v>
-      </c>
-      <c r="D36" s="4" t="s">
+      <c r="C36" s="4">
+        <v>0</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2610,10 +2623,10 @@
       <c r="B37" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="C37" s="3">
-        <v>0</v>
-      </c>
-      <c r="D37" s="4" t="s">
+      <c r="C37" s="4">
+        <v>0</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2624,10 +2637,10 @@
       <c r="B38" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="C38" s="3">
-        <v>0</v>
-      </c>
-      <c r="D38" s="4" t="s">
+      <c r="C38" s="4">
+        <v>0</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2638,10 +2651,10 @@
       <c r="B39" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="C39" s="3">
-        <v>0</v>
-      </c>
-      <c r="D39" s="4" t="s">
+      <c r="C39" s="4">
+        <v>0</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2652,10 +2665,10 @@
       <c r="B40" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="C40" s="3">
-        <v>0</v>
-      </c>
-      <c r="D40" s="4" t="s">
+      <c r="C40" s="4">
+        <v>0</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2666,10 +2679,10 @@
       <c r="B41" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="C41" s="3">
-        <v>0</v>
-      </c>
-      <c r="D41" s="4" t="s">
+      <c r="C41" s="4">
+        <v>0</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2680,10 +2693,10 @@
       <c r="B42" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="C42" s="3">
-        <v>0</v>
-      </c>
-      <c r="D42" s="4" t="s">
+      <c r="C42" s="4">
+        <v>0</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2694,10 +2707,10 @@
       <c r="B43" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="C43" s="3">
-        <v>0</v>
-      </c>
-      <c r="D43" s="4" t="s">
+      <c r="C43" s="4">
+        <v>0</v>
+      </c>
+      <c r="D43" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2708,10 +2721,10 @@
       <c r="B44" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="C44" s="3">
-        <v>0</v>
-      </c>
-      <c r="D44" s="4" t="s">
+      <c r="C44" s="4">
+        <v>0</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2722,10 +2735,10 @@
       <c r="B45" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="C45" s="3">
-        <v>0</v>
-      </c>
-      <c r="D45" s="4" t="s">
+      <c r="C45" s="4">
+        <v>0</v>
+      </c>
+      <c r="D45" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2736,10 +2749,10 @@
       <c r="B46" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="C46" s="3">
-        <v>0</v>
-      </c>
-      <c r="D46" s="4" t="s">
+      <c r="C46" s="4">
+        <v>0</v>
+      </c>
+      <c r="D46" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2750,10 +2763,10 @@
       <c r="B47" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="C47" s="3">
-        <v>0</v>
-      </c>
-      <c r="D47" s="4" t="s">
+      <c r="C47" s="4">
+        <v>0</v>
+      </c>
+      <c r="D47" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2764,10 +2777,10 @@
       <c r="B48" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="C48" s="3">
-        <v>0</v>
-      </c>
-      <c r="D48" s="4" t="s">
+      <c r="C48" s="4">
+        <v>0</v>
+      </c>
+      <c r="D48" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2778,10 +2791,10 @@
       <c r="B49" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="C49" s="3">
-        <v>0</v>
-      </c>
-      <c r="D49" s="4" t="s">
+      <c r="C49" s="4">
+        <v>0</v>
+      </c>
+      <c r="D49" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2792,10 +2805,10 @@
       <c r="B50" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="C50" s="3">
-        <v>0</v>
-      </c>
-      <c r="D50" s="4" t="s">
+      <c r="C50" s="4">
+        <v>0</v>
+      </c>
+      <c r="D50" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2806,10 +2819,10 @@
       <c r="B51" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="C51" s="3">
-        <v>0</v>
-      </c>
-      <c r="D51" s="4" t="s">
+      <c r="C51" s="4">
+        <v>0</v>
+      </c>
+      <c r="D51" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2820,10 +2833,10 @@
       <c r="B52" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="C52" s="3">
-        <v>0</v>
-      </c>
-      <c r="D52" s="4" t="s">
+      <c r="C52" s="4">
+        <v>0</v>
+      </c>
+      <c r="D52" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2834,10 +2847,10 @@
       <c r="B53" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="C53" s="3">
-        <v>0</v>
-      </c>
-      <c r="D53" s="4" t="s">
+      <c r="C53" s="4">
+        <v>0</v>
+      </c>
+      <c r="D53" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2848,10 +2861,10 @@
       <c r="B54" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="C54" s="3">
-        <v>0</v>
-      </c>
-      <c r="D54" s="4" t="s">
+      <c r="C54" s="4">
+        <v>0</v>
+      </c>
+      <c r="D54" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2862,10 +2875,10 @@
       <c r="B55" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="C55" s="3">
-        <v>0</v>
-      </c>
-      <c r="D55" s="4" t="s">
+      <c r="C55" s="4">
+        <v>0</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2876,10 +2889,10 @@
       <c r="B56" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="C56" s="3">
-        <v>0</v>
-      </c>
-      <c r="D56" s="4" t="s">
+      <c r="C56" s="4">
+        <v>0</v>
+      </c>
+      <c r="D56" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2890,10 +2903,10 @@
       <c r="B57" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="C57" s="3">
-        <v>0</v>
-      </c>
-      <c r="D57" s="4" t="s">
+      <c r="C57" s="4">
+        <v>0</v>
+      </c>
+      <c r="D57" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2904,10 +2917,10 @@
       <c r="B58" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="C58" s="3">
-        <v>0</v>
-      </c>
-      <c r="D58" s="4" t="s">
+      <c r="C58" s="4">
+        <v>0</v>
+      </c>
+      <c r="D58" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2918,10 +2931,10 @@
       <c r="B59" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="C59" s="3">
-        <v>0</v>
-      </c>
-      <c r="D59" s="4" t="s">
+      <c r="C59" s="4">
+        <v>0</v>
+      </c>
+      <c r="D59" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2932,10 +2945,10 @@
       <c r="B60" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="C60" s="3">
-        <v>0</v>
-      </c>
-      <c r="D60" s="4" t="s">
+      <c r="C60" s="4">
+        <v>0</v>
+      </c>
+      <c r="D60" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2946,10 +2959,10 @@
       <c r="B61" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="C61" s="3">
-        <v>0</v>
-      </c>
-      <c r="D61" s="4" t="s">
+      <c r="C61" s="4">
+        <v>0</v>
+      </c>
+      <c r="D61" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2960,10 +2973,10 @@
       <c r="B62" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="C62" s="3">
-        <v>0</v>
-      </c>
-      <c r="D62" s="4" t="s">
+      <c r="C62" s="4">
+        <v>0</v>
+      </c>
+      <c r="D62" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2974,10 +2987,10 @@
       <c r="B63" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="C63" s="3">
-        <v>0</v>
-      </c>
-      <c r="D63" s="4" t="s">
+      <c r="C63" s="4">
+        <v>0</v>
+      </c>
+      <c r="D63" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2988,10 +3001,10 @@
       <c r="B64" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="3">
-        <v>0</v>
-      </c>
-      <c r="D64" s="4" t="s">
+      <c r="C64" s="4">
+        <v>0</v>
+      </c>
+      <c r="D64" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3002,10 +3015,10 @@
       <c r="B65" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="C65" s="3">
-        <v>0</v>
-      </c>
-      <c r="D65" s="4" t="s">
+      <c r="C65" s="4">
+        <v>0</v>
+      </c>
+      <c r="D65" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3016,10 +3029,10 @@
       <c r="B66" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="C66" s="3">
-        <v>0</v>
-      </c>
-      <c r="D66" s="4" t="s">
+      <c r="C66" s="4">
+        <v>0</v>
+      </c>
+      <c r="D66" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3030,10 +3043,10 @@
       <c r="B67" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="C67" s="3">
-        <v>0</v>
-      </c>
-      <c r="D67" s="4" t="s">
+      <c r="C67" s="4">
+        <v>0</v>
+      </c>
+      <c r="D67" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3044,10 +3057,10 @@
       <c r="B68" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="C68" s="3">
-        <v>0</v>
-      </c>
-      <c r="D68" s="4" t="s">
+      <c r="C68" s="4">
+        <v>0</v>
+      </c>
+      <c r="D68" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3058,10 +3071,10 @@
       <c r="B69" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="C69" s="3">
-        <v>0</v>
-      </c>
-      <c r="D69" s="4" t="s">
+      <c r="C69" s="4">
+        <v>0</v>
+      </c>
+      <c r="D69" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3072,10 +3085,10 @@
       <c r="B70" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="C70" s="3">
-        <v>0</v>
-      </c>
-      <c r="D70" s="4" t="s">
+      <c r="C70" s="4">
+        <v>0</v>
+      </c>
+      <c r="D70" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3086,10 +3099,10 @@
       <c r="B71" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="C71" s="3">
-        <v>0</v>
-      </c>
-      <c r="D71" s="4" t="s">
+      <c r="C71" s="4">
+        <v>0</v>
+      </c>
+      <c r="D71" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3100,10 +3113,10 @@
       <c r="B72" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="C72" s="3">
-        <v>0</v>
-      </c>
-      <c r="D72" s="4" t="s">
+      <c r="C72" s="4">
+        <v>0</v>
+      </c>
+      <c r="D72" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3114,10 +3127,10 @@
       <c r="B73" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="C73" s="3">
-        <v>0</v>
-      </c>
-      <c r="D73" s="4" t="s">
+      <c r="C73" s="4">
+        <v>0</v>
+      </c>
+      <c r="D73" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3128,10 +3141,10 @@
       <c r="B74" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="C74" s="3">
-        <v>0</v>
-      </c>
-      <c r="D74" s="4" t="s">
+      <c r="C74" s="4">
+        <v>0</v>
+      </c>
+      <c r="D74" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3142,10 +3155,10 @@
       <c r="B75" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="C75" s="3">
-        <v>0</v>
-      </c>
-      <c r="D75" s="4" t="s">
+      <c r="C75" s="4">
+        <v>0</v>
+      </c>
+      <c r="D75" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3156,10 +3169,10 @@
       <c r="B76" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="C76" s="3">
-        <v>0</v>
-      </c>
-      <c r="D76" s="4" t="s">
+      <c r="C76" s="4">
+        <v>0</v>
+      </c>
+      <c r="D76" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3170,10 +3183,10 @@
       <c r="B77" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="C77" s="3">
-        <v>0</v>
-      </c>
-      <c r="D77" s="4" t="s">
+      <c r="C77" s="4">
+        <v>0</v>
+      </c>
+      <c r="D77" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3184,10 +3197,10 @@
       <c r="B78" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="C78" s="3">
-        <v>0</v>
-      </c>
-      <c r="D78" s="4" t="s">
+      <c r="C78" s="4">
+        <v>0</v>
+      </c>
+      <c r="D78" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3198,10 +3211,10 @@
       <c r="B79" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="C79" s="3">
-        <v>0</v>
-      </c>
-      <c r="D79" s="4" t="s">
+      <c r="C79" s="4">
+        <v>0</v>
+      </c>
+      <c r="D79" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3212,10 +3225,10 @@
       <c r="B80" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="C80" s="3">
-        <v>0</v>
-      </c>
-      <c r="D80" s="4" t="s">
+      <c r="C80" s="4">
+        <v>0</v>
+      </c>
+      <c r="D80" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3226,10 +3239,10 @@
       <c r="B81" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="C81" s="3">
-        <v>0</v>
-      </c>
-      <c r="D81" s="4" t="s">
+      <c r="C81" s="4">
+        <v>0</v>
+      </c>
+      <c r="D81" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3240,10 +3253,10 @@
       <c r="B82" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="C82" s="3">
-        <v>0</v>
-      </c>
-      <c r="D82" s="4" t="s">
+      <c r="C82" s="4">
+        <v>0</v>
+      </c>
+      <c r="D82" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3254,10 +3267,10 @@
       <c r="B83" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="C83" s="3">
-        <v>0</v>
-      </c>
-      <c r="D83" s="4" t="s">
+      <c r="C83" s="4">
+        <v>0</v>
+      </c>
+      <c r="D83" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3268,10 +3281,10 @@
       <c r="B84" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="C84" s="3">
-        <v>0</v>
-      </c>
-      <c r="D84" s="4" t="s">
+      <c r="C84" s="4">
+        <v>0</v>
+      </c>
+      <c r="D84" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3282,10 +3295,10 @@
       <c r="B85" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="C85" s="3">
-        <v>0</v>
-      </c>
-      <c r="D85" s="4" t="s">
+      <c r="C85" s="4">
+        <v>0</v>
+      </c>
+      <c r="D85" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3296,10 +3309,10 @@
       <c r="B86" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="C86" s="3">
-        <v>0</v>
-      </c>
-      <c r="D86" s="4" t="s">
+      <c r="C86" s="4">
+        <v>0</v>
+      </c>
+      <c r="D86" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3310,10 +3323,10 @@
       <c r="B87" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="C87" s="3">
-        <v>0</v>
-      </c>
-      <c r="D87" s="4" t="s">
+      <c r="C87" s="4">
+        <v>0</v>
+      </c>
+      <c r="D87" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3324,10 +3337,10 @@
       <c r="B88" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="C88" s="3">
-        <v>0</v>
-      </c>
-      <c r="D88" s="4" t="s">
+      <c r="C88" s="4">
+        <v>0</v>
+      </c>
+      <c r="D88" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3338,10 +3351,10 @@
       <c r="B89" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="C89" s="3">
-        <v>0</v>
-      </c>
-      <c r="D89" s="4" t="s">
+      <c r="C89" s="4">
+        <v>0</v>
+      </c>
+      <c r="D89" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3352,10 +3365,10 @@
       <c r="B90" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="C90" s="3">
-        <v>0</v>
-      </c>
-      <c r="D90" s="4" t="s">
+      <c r="C90" s="4">
+        <v>0</v>
+      </c>
+      <c r="D90" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3366,10 +3379,10 @@
       <c r="B91" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="C91" s="3">
-        <v>0</v>
-      </c>
-      <c r="D91" s="4" t="s">
+      <c r="C91" s="4">
+        <v>0</v>
+      </c>
+      <c r="D91" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3380,10 +3393,10 @@
       <c r="B92" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="C92" s="3">
-        <v>0</v>
-      </c>
-      <c r="D92" s="4" t="s">
+      <c r="C92" s="4">
+        <v>0</v>
+      </c>
+      <c r="D92" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3394,10 +3407,10 @@
       <c r="B93" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="C93" s="3">
-        <v>0</v>
-      </c>
-      <c r="D93" s="4" t="s">
+      <c r="C93" s="4">
+        <v>0</v>
+      </c>
+      <c r="D93" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3408,10 +3421,10 @@
       <c r="B94" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="C94" s="3">
-        <v>0</v>
-      </c>
-      <c r="D94" s="4" t="s">
+      <c r="C94" s="4">
+        <v>0</v>
+      </c>
+      <c r="D94" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3422,10 +3435,10 @@
       <c r="B95" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="C95" s="3">
-        <v>0</v>
-      </c>
-      <c r="D95" s="4" t="s">
+      <c r="C95" s="4">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3436,10 +3449,10 @@
       <c r="B96" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="C96" s="3">
-        <v>0</v>
-      </c>
-      <c r="D96" s="4" t="s">
+      <c r="C96" s="4">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3450,10 +3463,10 @@
       <c r="B97" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="C97" s="3">
-        <v>0</v>
-      </c>
-      <c r="D97" s="4" t="s">
+      <c r="C97" s="4">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3464,10 +3477,10 @@
       <c r="B98" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="C98" s="3">
-        <v>0</v>
-      </c>
-      <c r="D98" s="4" t="s">
+      <c r="C98" s="4">
+        <v>0</v>
+      </c>
+      <c r="D98" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3478,10 +3491,10 @@
       <c r="B99" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="C99" s="3">
-        <v>0</v>
-      </c>
-      <c r="D99" s="4" t="s">
+      <c r="C99" s="4">
+        <v>0</v>
+      </c>
+      <c r="D99" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3492,10 +3505,10 @@
       <c r="B100" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="C100" s="3">
-        <v>0</v>
-      </c>
-      <c r="D100" s="4" t="s">
+      <c r="C100" s="4">
+        <v>0</v>
+      </c>
+      <c r="D100" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3506,10 +3519,10 @@
       <c r="B101" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C101" s="3">
-        <v>0</v>
-      </c>
-      <c r="D101" s="4" t="s">
+      <c r="C101" s="4">
+        <v>0</v>
+      </c>
+      <c r="D101" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3520,10 +3533,10 @@
       <c r="B102" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="C102" s="3">
-        <v>0</v>
-      </c>
-      <c r="D102" s="4" t="s">
+      <c r="C102" s="4">
+        <v>0</v>
+      </c>
+      <c r="D102" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3534,10 +3547,10 @@
       <c r="B103" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="C103" s="3">
-        <v>0</v>
-      </c>
-      <c r="D103" s="4" t="s">
+      <c r="C103" s="4">
+        <v>0</v>
+      </c>
+      <c r="D103" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3548,10 +3561,10 @@
       <c r="B104" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="C104" s="3">
-        <v>0</v>
-      </c>
-      <c r="D104" s="4" t="s">
+      <c r="C104" s="4">
+        <v>0</v>
+      </c>
+      <c r="D104" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3562,10 +3575,10 @@
       <c r="B105" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="C105" s="3">
-        <v>0</v>
-      </c>
-      <c r="D105" s="4" t="s">
+      <c r="C105" s="4">
+        <v>0</v>
+      </c>
+      <c r="D105" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3576,10 +3589,10 @@
       <c r="B106" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="C106" s="3">
-        <v>0</v>
-      </c>
-      <c r="D106" s="4" t="s">
+      <c r="C106" s="4">
+        <v>0</v>
+      </c>
+      <c r="D106" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3590,10 +3603,10 @@
       <c r="B107" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="C107" s="3">
-        <v>0</v>
-      </c>
-      <c r="D107" s="4" t="s">
+      <c r="C107" s="4">
+        <v>0</v>
+      </c>
+      <c r="D107" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3604,10 +3617,10 @@
       <c r="B108" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="C108" s="3">
-        <v>0</v>
-      </c>
-      <c r="D108" s="4" t="s">
+      <c r="C108" s="4">
+        <v>0</v>
+      </c>
+      <c r="D108" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3618,10 +3631,10 @@
       <c r="B109" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="C109" s="3">
-        <v>0</v>
-      </c>
-      <c r="D109" s="4" t="s">
+      <c r="C109" s="4">
+        <v>0</v>
+      </c>
+      <c r="D109" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3632,10 +3645,10 @@
       <c r="B110" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="C110" s="3">
-        <v>0</v>
-      </c>
-      <c r="D110" s="4" t="s">
+      <c r="C110" s="4">
+        <v>0</v>
+      </c>
+      <c r="D110" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3646,10 +3659,10 @@
       <c r="B111" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="C111" s="3">
-        <v>0</v>
-      </c>
-      <c r="D111" s="4" t="s">
+      <c r="C111" s="4">
+        <v>0</v>
+      </c>
+      <c r="D111" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3660,10 +3673,10 @@
       <c r="B112" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="C112" s="3">
-        <v>0</v>
-      </c>
-      <c r="D112" s="4" t="s">
+      <c r="C112" s="4">
+        <v>0</v>
+      </c>
+      <c r="D112" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3674,10 +3687,10 @@
       <c r="B113" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="C113" s="3">
-        <v>0</v>
-      </c>
-      <c r="D113" s="4" t="s">
+      <c r="C113" s="4">
+        <v>0</v>
+      </c>
+      <c r="D113" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3688,10 +3701,10 @@
       <c r="B114" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="C114" s="3">
-        <v>0</v>
-      </c>
-      <c r="D114" s="4" t="s">
+      <c r="C114" s="4">
+        <v>0</v>
+      </c>
+      <c r="D114" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3702,10 +3715,10 @@
       <c r="B115" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="C115" s="3">
-        <v>0</v>
-      </c>
-      <c r="D115" s="4" t="s">
+      <c r="C115" s="4">
+        <v>0</v>
+      </c>
+      <c r="D115" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3716,10 +3729,10 @@
       <c r="B116" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="C116" s="3">
-        <v>0</v>
-      </c>
-      <c r="D116" s="4" t="s">
+      <c r="C116" s="4">
+        <v>0</v>
+      </c>
+      <c r="D116" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3730,10 +3743,10 @@
       <c r="B117" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="C117" s="3">
-        <v>0</v>
-      </c>
-      <c r="D117" s="4" t="s">
+      <c r="C117" s="4">
+        <v>0</v>
+      </c>
+      <c r="D117" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3744,10 +3757,10 @@
       <c r="B118" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="C118" s="3">
-        <v>0</v>
-      </c>
-      <c r="D118" s="4" t="s">
+      <c r="C118" s="4">
+        <v>0</v>
+      </c>
+      <c r="D118" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3758,10 +3771,10 @@
       <c r="B119" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="C119" s="3">
-        <v>0</v>
-      </c>
-      <c r="D119" s="4" t="s">
+      <c r="C119" s="4">
+        <v>0</v>
+      </c>
+      <c r="D119" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3772,10 +3785,10 @@
       <c r="B120" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="C120" s="3">
-        <v>0</v>
-      </c>
-      <c r="D120" s="4" t="s">
+      <c r="C120" s="4">
+        <v>0</v>
+      </c>
+      <c r="D120" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3786,10 +3799,10 @@
       <c r="B121" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="C121" s="3">
-        <v>0</v>
-      </c>
-      <c r="D121" s="4" t="s">
+      <c r="C121" s="4">
+        <v>0</v>
+      </c>
+      <c r="D121" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3800,10 +3813,10 @@
       <c r="B122" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="C122" s="3">
-        <v>0</v>
-      </c>
-      <c r="D122" s="4" t="s">
+      <c r="C122" s="4">
+        <v>0</v>
+      </c>
+      <c r="D122" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3814,10 +3827,10 @@
       <c r="B123" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="C123" s="3">
-        <v>0</v>
-      </c>
-      <c r="D123" s="4" t="s">
+      <c r="C123" s="4">
+        <v>0</v>
+      </c>
+      <c r="D123" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3828,10 +3841,10 @@
       <c r="B124" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="C124" s="3">
-        <v>0</v>
-      </c>
-      <c r="D124" s="4" t="s">
+      <c r="C124" s="4">
+        <v>0</v>
+      </c>
+      <c r="D124" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3842,10 +3855,10 @@
       <c r="B125" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="C125" s="3">
-        <v>0</v>
-      </c>
-      <c r="D125" s="4" t="s">
+      <c r="C125" s="4">
+        <v>0</v>
+      </c>
+      <c r="D125" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3856,10 +3869,10 @@
       <c r="B126" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="C126" s="3">
-        <v>0</v>
-      </c>
-      <c r="D126" s="4" t="s">
+      <c r="C126" s="4">
+        <v>0</v>
+      </c>
+      <c r="D126" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3870,10 +3883,10 @@
       <c r="B127" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="C127" s="3">
-        <v>0</v>
-      </c>
-      <c r="D127" s="4" t="s">
+      <c r="C127" s="4">
+        <v>0</v>
+      </c>
+      <c r="D127" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3884,10 +3897,10 @@
       <c r="B128" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="C128" s="3">
-        <v>0</v>
-      </c>
-      <c r="D128" s="4" t="s">
+      <c r="C128" s="4">
+        <v>0</v>
+      </c>
+      <c r="D128" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3898,10 +3911,10 @@
       <c r="B129" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="C129" s="3">
-        <v>0</v>
-      </c>
-      <c r="D129" s="4" t="s">
+      <c r="C129" s="4">
+        <v>0</v>
+      </c>
+      <c r="D129" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3912,10 +3925,10 @@
       <c r="B130" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="C130" s="3">
-        <v>0</v>
-      </c>
-      <c r="D130" s="4" t="s">
+      <c r="C130" s="4">
+        <v>0</v>
+      </c>
+      <c r="D130" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3926,10 +3939,10 @@
       <c r="B131" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="C131" s="3">
-        <v>0</v>
-      </c>
-      <c r="D131" s="4" t="s">
+      <c r="C131" s="4">
+        <v>0</v>
+      </c>
+      <c r="D131" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3940,10 +3953,10 @@
       <c r="B132" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="C132" s="3">
-        <v>0</v>
-      </c>
-      <c r="D132" s="4" t="s">
+      <c r="C132" s="4">
+        <v>0</v>
+      </c>
+      <c r="D132" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3954,10 +3967,10 @@
       <c r="B133" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="C133" s="3">
-        <v>0</v>
-      </c>
-      <c r="D133" s="4" t="s">
+      <c r="C133" s="4">
+        <v>0</v>
+      </c>
+      <c r="D133" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3968,10 +3981,10 @@
       <c r="B134" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="C134" s="3">
-        <v>0</v>
-      </c>
-      <c r="D134" s="4" t="s">
+      <c r="C134" s="4">
+        <v>0</v>
+      </c>
+      <c r="D134" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3982,10 +3995,10 @@
       <c r="B135" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="C135" s="3">
-        <v>0</v>
-      </c>
-      <c r="D135" s="4" t="s">
+      <c r="C135" s="4">
+        <v>0</v>
+      </c>
+      <c r="D135" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3996,10 +4009,10 @@
       <c r="B136" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="C136" s="3">
-        <v>0</v>
-      </c>
-      <c r="D136" s="4" t="s">
+      <c r="C136" s="4">
+        <v>0</v>
+      </c>
+      <c r="D136" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4010,10 +4023,10 @@
       <c r="B137" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="C137" s="3">
-        <v>0</v>
-      </c>
-      <c r="D137" s="4" t="s">
+      <c r="C137" s="4">
+        <v>0</v>
+      </c>
+      <c r="D137" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4024,10 +4037,10 @@
       <c r="B138" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="C138" s="3">
-        <v>0</v>
-      </c>
-      <c r="D138" s="4" t="s">
+      <c r="C138" s="4">
+        <v>0</v>
+      </c>
+      <c r="D138" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4038,10 +4051,10 @@
       <c r="B139" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="C139" s="3">
-        <v>0</v>
-      </c>
-      <c r="D139" s="4" t="s">
+      <c r="C139" s="4">
+        <v>0</v>
+      </c>
+      <c r="D139" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4052,10 +4065,10 @@
       <c r="B140" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="C140" s="3">
-        <v>0</v>
-      </c>
-      <c r="D140" s="4" t="s">
+      <c r="C140" s="4">
+        <v>0</v>
+      </c>
+      <c r="D140" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4066,10 +4079,10 @@
       <c r="B141" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="C141" s="3">
-        <v>0</v>
-      </c>
-      <c r="D141" s="4" t="s">
+      <c r="C141" s="4">
+        <v>0</v>
+      </c>
+      <c r="D141" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4080,10 +4093,10 @@
       <c r="B142" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="C142" s="3">
-        <v>0</v>
-      </c>
-      <c r="D142" s="4" t="s">
+      <c r="C142" s="4">
+        <v>0</v>
+      </c>
+      <c r="D142" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4094,10 +4107,10 @@
       <c r="B143" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="C143" s="3">
-        <v>0</v>
-      </c>
-      <c r="D143" s="4" t="s">
+      <c r="C143" s="4">
+        <v>0</v>
+      </c>
+      <c r="D143" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4108,10 +4121,10 @@
       <c r="B144" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="C144" s="3">
-        <v>0</v>
-      </c>
-      <c r="D144" s="4" t="s">
+      <c r="C144" s="4">
+        <v>0</v>
+      </c>
+      <c r="D144" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4122,10 +4135,10 @@
       <c r="B145" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="C145" s="3">
-        <v>0</v>
-      </c>
-      <c r="D145" s="4" t="s">
+      <c r="C145" s="4">
+        <v>0</v>
+      </c>
+      <c r="D145" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4136,10 +4149,10 @@
       <c r="B146" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="C146" s="3">
-        <v>0</v>
-      </c>
-      <c r="D146" s="4" t="s">
+      <c r="C146" s="4">
+        <v>0</v>
+      </c>
+      <c r="D146" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4150,10 +4163,10 @@
       <c r="B147" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="C147" s="3">
-        <v>0</v>
-      </c>
-      <c r="D147" s="4" t="s">
+      <c r="C147" s="4">
+        <v>0</v>
+      </c>
+      <c r="D147" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4164,10 +4177,10 @@
       <c r="B148" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="C148" s="3">
-        <v>0</v>
-      </c>
-      <c r="D148" s="4" t="s">
+      <c r="C148" s="4">
+        <v>0</v>
+      </c>
+      <c r="D148" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4178,10 +4191,10 @@
       <c r="B149" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="C149" s="3">
-        <v>0</v>
-      </c>
-      <c r="D149" s="4" t="s">
+      <c r="C149" s="4">
+        <v>0</v>
+      </c>
+      <c r="D149" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4192,10 +4205,10 @@
       <c r="B150" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="C150" s="3">
-        <v>0</v>
-      </c>
-      <c r="D150" s="4" t="s">
+      <c r="C150" s="4">
+        <v>0</v>
+      </c>
+      <c r="D150" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4206,10 +4219,10 @@
       <c r="B151" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="C151" s="3">
-        <v>0</v>
-      </c>
-      <c r="D151" s="4" t="s">
+      <c r="C151" s="4">
+        <v>0</v>
+      </c>
+      <c r="D151" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4220,10 +4233,10 @@
       <c r="B152" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="C152" s="3">
-        <v>0</v>
-      </c>
-      <c r="D152" s="4" t="s">
+      <c r="C152" s="4">
+        <v>0</v>
+      </c>
+      <c r="D152" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4234,10 +4247,10 @@
       <c r="B153" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="C153" s="3">
-        <v>0</v>
-      </c>
-      <c r="D153" s="4" t="s">
+      <c r="C153" s="4">
+        <v>0</v>
+      </c>
+      <c r="D153" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4248,10 +4261,10 @@
       <c r="B154" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="C154" s="3">
-        <v>0</v>
-      </c>
-      <c r="D154" s="4" t="s">
+      <c r="C154" s="4">
+        <v>0</v>
+      </c>
+      <c r="D154" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4262,10 +4275,10 @@
       <c r="B155" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="C155" s="3">
-        <v>0</v>
-      </c>
-      <c r="D155" s="4" t="s">
+      <c r="C155" s="4">
+        <v>0</v>
+      </c>
+      <c r="D155" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4276,10 +4289,10 @@
       <c r="B156" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="C156" s="3">
-        <v>0</v>
-      </c>
-      <c r="D156" s="4" t="s">
+      <c r="C156" s="4">
+        <v>0</v>
+      </c>
+      <c r="D156" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4290,10 +4303,10 @@
       <c r="B157" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="C157" s="3">
-        <v>0</v>
-      </c>
-      <c r="D157" s="4" t="s">
+      <c r="C157" s="4">
+        <v>0</v>
+      </c>
+      <c r="D157" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4304,10 +4317,10 @@
       <c r="B158" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="C158" s="3">
-        <v>0</v>
-      </c>
-      <c r="D158" s="4" t="s">
+      <c r="C158" s="4">
+        <v>0</v>
+      </c>
+      <c r="D158" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4318,10 +4331,10 @@
       <c r="B159" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="C159" s="3">
-        <v>0</v>
-      </c>
-      <c r="D159" s="4" t="s">
+      <c r="C159" s="4">
+        <v>0</v>
+      </c>
+      <c r="D159" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4332,10 +4345,10 @@
       <c r="B160" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="C160" s="3">
-        <v>0</v>
-      </c>
-      <c r="D160" s="4" t="s">
+      <c r="C160" s="4">
+        <v>0</v>
+      </c>
+      <c r="D160" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4346,10 +4359,10 @@
       <c r="B161" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="C161" s="3">
-        <v>0</v>
-      </c>
-      <c r="D161" s="4" t="s">
+      <c r="C161" s="4">
+        <v>0</v>
+      </c>
+      <c r="D161" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4360,10 +4373,10 @@
       <c r="B162" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="C162" s="3">
-        <v>0</v>
-      </c>
-      <c r="D162" s="4" t="s">
+      <c r="C162" s="4">
+        <v>0</v>
+      </c>
+      <c r="D162" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4374,10 +4387,10 @@
       <c r="B163" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="C163" s="3">
-        <v>0</v>
-      </c>
-      <c r="D163" s="4" t="s">
+      <c r="C163" s="4">
+        <v>0</v>
+      </c>
+      <c r="D163" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4388,10 +4401,10 @@
       <c r="B164" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="C164" s="3">
-        <v>0</v>
-      </c>
-      <c r="D164" s="4" t="s">
+      <c r="C164" s="4">
+        <v>0</v>
+      </c>
+      <c r="D164" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4402,10 +4415,10 @@
       <c r="B165" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="C165" s="3">
-        <v>0</v>
-      </c>
-      <c r="D165" s="4" t="s">
+      <c r="C165" s="4">
+        <v>0</v>
+      </c>
+      <c r="D165" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4416,10 +4429,10 @@
       <c r="B166" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="C166" s="3">
-        <v>0</v>
-      </c>
-      <c r="D166" s="4" t="s">
+      <c r="C166" s="4">
+        <v>0</v>
+      </c>
+      <c r="D166" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4430,10 +4443,10 @@
       <c r="B167" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="C167" s="3">
-        <v>0</v>
-      </c>
-      <c r="D167" s="4" t="s">
+      <c r="C167" s="4">
+        <v>0</v>
+      </c>
+      <c r="D167" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4444,10 +4457,10 @@
       <c r="B168" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="C168" s="3">
-        <v>0</v>
-      </c>
-      <c r="D168" s="4" t="s">
+      <c r="C168" s="4">
+        <v>0</v>
+      </c>
+      <c r="D168" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4458,10 +4471,10 @@
       <c r="B169" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="C169" s="3">
-        <v>0</v>
-      </c>
-      <c r="D169" s="4" t="s">
+      <c r="C169" s="4">
+        <v>0</v>
+      </c>
+      <c r="D169" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4472,10 +4485,10 @@
       <c r="B170" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="C170" s="3">
-        <v>0</v>
-      </c>
-      <c r="D170" s="4" t="s">
+      <c r="C170" s="4">
+        <v>0</v>
+      </c>
+      <c r="D170" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4486,10 +4499,10 @@
       <c r="B171" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="C171" s="3">
-        <v>0</v>
-      </c>
-      <c r="D171" s="4" t="s">
+      <c r="C171" s="4">
+        <v>0</v>
+      </c>
+      <c r="D171" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4500,10 +4513,10 @@
       <c r="B172" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="C172" s="3">
-        <v>0</v>
-      </c>
-      <c r="D172" s="4" t="s">
+      <c r="C172" s="4">
+        <v>0</v>
+      </c>
+      <c r="D172" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4514,10 +4527,10 @@
       <c r="B173" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="C173" s="3">
-        <v>0</v>
-      </c>
-      <c r="D173" s="4" t="s">
+      <c r="C173" s="4">
+        <v>0</v>
+      </c>
+      <c r="D173" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4528,10 +4541,10 @@
       <c r="B174" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="C174" s="3">
-        <v>0</v>
-      </c>
-      <c r="D174" s="4" t="s">
+      <c r="C174" s="4">
+        <v>0</v>
+      </c>
+      <c r="D174" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4542,10 +4555,10 @@
       <c r="B175" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="C175" s="3">
-        <v>0</v>
-      </c>
-      <c r="D175" s="4" t="s">
+      <c r="C175" s="4">
+        <v>0</v>
+      </c>
+      <c r="D175" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4556,10 +4569,10 @@
       <c r="B176" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="C176" s="3">
-        <v>0</v>
-      </c>
-      <c r="D176" s="4" t="s">
+      <c r="C176" s="4">
+        <v>0</v>
+      </c>
+      <c r="D176" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4570,10 +4583,10 @@
       <c r="B177" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="C177" s="3">
-        <v>0</v>
-      </c>
-      <c r="D177" s="4" t="s">
+      <c r="C177" s="4">
+        <v>0</v>
+      </c>
+      <c r="D177" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4584,10 +4597,10 @@
       <c r="B178" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="C178" s="3">
-        <v>0</v>
-      </c>
-      <c r="D178" s="4" t="s">
+      <c r="C178" s="4">
+        <v>0</v>
+      </c>
+      <c r="D178" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4598,10 +4611,10 @@
       <c r="B179" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="C179" s="3">
-        <v>0</v>
-      </c>
-      <c r="D179" s="4" t="s">
+      <c r="C179" s="4">
+        <v>0</v>
+      </c>
+      <c r="D179" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4612,10 +4625,10 @@
       <c r="B180" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="C180" s="3">
-        <v>0</v>
-      </c>
-      <c r="D180" s="4" t="s">
+      <c r="C180" s="4">
+        <v>0</v>
+      </c>
+      <c r="D180" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4626,10 +4639,10 @@
       <c r="B181" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="C181" s="3">
-        <v>0</v>
-      </c>
-      <c r="D181" s="4" t="s">
+      <c r="C181" s="4">
+        <v>0</v>
+      </c>
+      <c r="D181" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4640,10 +4653,10 @@
       <c r="B182" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="C182" s="3">
-        <v>0</v>
-      </c>
-      <c r="D182" s="4" t="s">
+      <c r="C182" s="4">
+        <v>0</v>
+      </c>
+      <c r="D182" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4654,10 +4667,10 @@
       <c r="B183" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="C183" s="3">
-        <v>0</v>
-      </c>
-      <c r="D183" s="4" t="s">
+      <c r="C183" s="4">
+        <v>0</v>
+      </c>
+      <c r="D183" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4668,10 +4681,10 @@
       <c r="B184" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="C184" s="3">
-        <v>0</v>
-      </c>
-      <c r="D184" s="4" t="s">
+      <c r="C184" s="4">
+        <v>0</v>
+      </c>
+      <c r="D184" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4682,10 +4695,10 @@
       <c r="B185" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="C185" s="3">
-        <v>0</v>
-      </c>
-      <c r="D185" s="4" t="s">
+      <c r="C185" s="4">
+        <v>0</v>
+      </c>
+      <c r="D185" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4696,10 +4709,10 @@
       <c r="B186" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="C186" s="3">
-        <v>0</v>
-      </c>
-      <c r="D186" s="4" t="s">
+      <c r="C186" s="4">
+        <v>0</v>
+      </c>
+      <c r="D186" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4710,10 +4723,10 @@
       <c r="B187" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="C187" s="3">
-        <v>0</v>
-      </c>
-      <c r="D187" s="4" t="s">
+      <c r="C187" s="4">
+        <v>0</v>
+      </c>
+      <c r="D187" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4724,10 +4737,10 @@
       <c r="B188" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="C188" s="3">
-        <v>0</v>
-      </c>
-      <c r="D188" s="4" t="s">
+      <c r="C188" s="4">
+        <v>0</v>
+      </c>
+      <c r="D188" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4738,10 +4751,10 @@
       <c r="B189" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="C189" s="3">
-        <v>0</v>
-      </c>
-      <c r="D189" s="4" t="s">
+      <c r="C189" s="4">
+        <v>0</v>
+      </c>
+      <c r="D189" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4752,10 +4765,10 @@
       <c r="B190" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="C190" s="3">
-        <v>0</v>
-      </c>
-      <c r="D190" s="4" t="s">
+      <c r="C190" s="4">
+        <v>0</v>
+      </c>
+      <c r="D190" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4766,10 +4779,10 @@
       <c r="B191" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="C191" s="3">
-        <v>0</v>
-      </c>
-      <c r="D191" s="4" t="s">
+      <c r="C191" s="4">
+        <v>0</v>
+      </c>
+      <c r="D191" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4780,10 +4793,10 @@
       <c r="B192" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="C192" s="3">
-        <v>0</v>
-      </c>
-      <c r="D192" s="4" t="s">
+      <c r="C192" s="4">
+        <v>0</v>
+      </c>
+      <c r="D192" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4794,10 +4807,10 @@
       <c r="B193" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="C193" s="3">
-        <v>0</v>
-      </c>
-      <c r="D193" s="4" t="s">
+      <c r="C193" s="4">
+        <v>0</v>
+      </c>
+      <c r="D193" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4808,10 +4821,10 @@
       <c r="B194" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="C194" s="3">
-        <v>0</v>
-      </c>
-      <c r="D194" s="4" t="s">
+      <c r="C194" s="4">
+        <v>0</v>
+      </c>
+      <c r="D194" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4822,10 +4835,10 @@
       <c r="B195" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="C195" s="3">
-        <v>0</v>
-      </c>
-      <c r="D195" s="4" t="s">
+      <c r="C195" s="4">
+        <v>0</v>
+      </c>
+      <c r="D195" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4836,10 +4849,10 @@
       <c r="B196" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="C196" s="3">
-        <v>0</v>
-      </c>
-      <c r="D196" s="4" t="s">
+      <c r="C196" s="4">
+        <v>0</v>
+      </c>
+      <c r="D196" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4850,10 +4863,10 @@
       <c r="B197" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="C197" s="3">
-        <v>0</v>
-      </c>
-      <c r="D197" s="4" t="s">
+      <c r="C197" s="4">
+        <v>0</v>
+      </c>
+      <c r="D197" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4864,10 +4877,10 @@
       <c r="B198" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="C198" s="3">
-        <v>0</v>
-      </c>
-      <c r="D198" s="4" t="s">
+      <c r="C198" s="4">
+        <v>0</v>
+      </c>
+      <c r="D198" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4878,10 +4891,10 @@
       <c r="B199" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="C199" s="3">
-        <v>0</v>
-      </c>
-      <c r="D199" s="4" t="s">
+      <c r="C199" s="4">
+        <v>0</v>
+      </c>
+      <c r="D199" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4892,10 +4905,10 @@
       <c r="B200" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="C200" s="3">
-        <v>0</v>
-      </c>
-      <c r="D200" s="4" t="s">
+      <c r="C200" s="4">
+        <v>0</v>
+      </c>
+      <c r="D200" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4906,10 +4919,10 @@
       <c r="B201" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="C201" s="3">
-        <v>0</v>
-      </c>
-      <c r="D201" s="4" t="s">
+      <c r="C201" s="4">
+        <v>0</v>
+      </c>
+      <c r="D201" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4920,10 +4933,10 @@
       <c r="B202" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="C202" s="3">
-        <v>0</v>
-      </c>
-      <c r="D202" s="4" t="s">
+      <c r="C202" s="4">
+        <v>0</v>
+      </c>
+      <c r="D202" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4934,10 +4947,10 @@
       <c r="B203" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="C203" s="3">
-        <v>0</v>
-      </c>
-      <c r="D203" s="4" t="s">
+      <c r="C203" s="4">
+        <v>0</v>
+      </c>
+      <c r="D203" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4948,10 +4961,10 @@
       <c r="B204" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="C204" s="3">
-        <v>0</v>
-      </c>
-      <c r="D204" s="4" t="s">
+      <c r="C204" s="4">
+        <v>0</v>
+      </c>
+      <c r="D204" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4962,10 +4975,10 @@
       <c r="B205" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="C205" s="3">
-        <v>0</v>
-      </c>
-      <c r="D205" s="4" t="s">
+      <c r="C205" s="4">
+        <v>0</v>
+      </c>
+      <c r="D205" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4976,10 +4989,10 @@
       <c r="B206" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="C206" s="3">
-        <v>0</v>
-      </c>
-      <c r="D206" s="4" t="s">
+      <c r="C206" s="4">
+        <v>0</v>
+      </c>
+      <c r="D206" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4990,10 +5003,10 @@
       <c r="B207" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="C207" s="3">
-        <v>0</v>
-      </c>
-      <c r="D207" s="4" t="s">
+      <c r="C207" s="4">
+        <v>0</v>
+      </c>
+      <c r="D207" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5004,10 +5017,10 @@
       <c r="B208" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="C208" s="3">
-        <v>0</v>
-      </c>
-      <c r="D208" s="4" t="s">
+      <c r="C208" s="4">
+        <v>0</v>
+      </c>
+      <c r="D208" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5018,10 +5031,10 @@
       <c r="B209" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="C209" s="3">
-        <v>0</v>
-      </c>
-      <c r="D209" s="4" t="s">
+      <c r="C209" s="4">
+        <v>0</v>
+      </c>
+      <c r="D209" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5032,10 +5045,10 @@
       <c r="B210" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="C210" s="3">
-        <v>0</v>
-      </c>
-      <c r="D210" s="4" t="s">
+      <c r="C210" s="4">
+        <v>0</v>
+      </c>
+      <c r="D210" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5046,10 +5059,10 @@
       <c r="B211" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="C211" s="3">
-        <v>0</v>
-      </c>
-      <c r="D211" s="4" t="s">
+      <c r="C211" s="4">
+        <v>0</v>
+      </c>
+      <c r="D211" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5060,10 +5073,10 @@
       <c r="B212" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="C212" s="3">
-        <v>0</v>
-      </c>
-      <c r="D212" s="4" t="s">
+      <c r="C212" s="4">
+        <v>0</v>
+      </c>
+      <c r="D212" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5074,10 +5087,10 @@
       <c r="B213" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="C213" s="3">
-        <v>0</v>
-      </c>
-      <c r="D213" s="4" t="s">
+      <c r="C213" s="4">
+        <v>0</v>
+      </c>
+      <c r="D213" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5088,10 +5101,10 @@
       <c r="B214" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="C214" s="3">
-        <v>0</v>
-      </c>
-      <c r="D214" s="4" t="s">
+      <c r="C214" s="4">
+        <v>0</v>
+      </c>
+      <c r="D214" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5102,10 +5115,10 @@
       <c r="B215" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="C215" s="3">
-        <v>0</v>
-      </c>
-      <c r="D215" s="4" t="s">
+      <c r="C215" s="4">
+        <v>0</v>
+      </c>
+      <c r="D215" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5116,10 +5129,10 @@
       <c r="B216" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="C216" s="3">
-        <v>0</v>
-      </c>
-      <c r="D216" s="4" t="s">
+      <c r="C216" s="4">
+        <v>0</v>
+      </c>
+      <c r="D216" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5130,10 +5143,10 @@
       <c r="B217" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="C217" s="3">
-        <v>0</v>
-      </c>
-      <c r="D217" s="4" t="s">
+      <c r="C217" s="4">
+        <v>0</v>
+      </c>
+      <c r="D217" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5144,10 +5157,10 @@
       <c r="B218" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="C218" s="3">
-        <v>0</v>
-      </c>
-      <c r="D218" s="4" t="s">
+      <c r="C218" s="4">
+        <v>0</v>
+      </c>
+      <c r="D218" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5158,10 +5171,10 @@
       <c r="B219" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="C219" s="3">
-        <v>0</v>
-      </c>
-      <c r="D219" s="4" t="s">
+      <c r="C219" s="4">
+        <v>0</v>
+      </c>
+      <c r="D219" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5172,10 +5185,10 @@
       <c r="B220" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="C220" s="3">
-        <v>0</v>
-      </c>
-      <c r="D220" s="4" t="s">
+      <c r="C220" s="4">
+        <v>0</v>
+      </c>
+      <c r="D220" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5186,10 +5199,10 @@
       <c r="B221" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="C221" s="3">
-        <v>0</v>
-      </c>
-      <c r="D221" s="4" t="s">
+      <c r="C221" s="4">
+        <v>0</v>
+      </c>
+      <c r="D221" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5200,10 +5213,10 @@
       <c r="B222" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="C222" s="3">
-        <v>0</v>
-      </c>
-      <c r="D222" s="4" t="s">
+      <c r="C222" s="4">
+        <v>0</v>
+      </c>
+      <c r="D222" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5214,10 +5227,10 @@
       <c r="B223" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="C223" s="3">
-        <v>0</v>
-      </c>
-      <c r="D223" s="4" t="s">
+      <c r="C223" s="4">
+        <v>0</v>
+      </c>
+      <c r="D223" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5228,10 +5241,10 @@
       <c r="B224" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="C224" s="3">
-        <v>0</v>
-      </c>
-      <c r="D224" s="4" t="s">
+      <c r="C224" s="4">
+        <v>0</v>
+      </c>
+      <c r="D224" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5242,10 +5255,10 @@
       <c r="B225" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="C225" s="3">
-        <v>0</v>
-      </c>
-      <c r="D225" s="4" t="s">
+      <c r="C225" s="4">
+        <v>0</v>
+      </c>
+      <c r="D225" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5256,10 +5269,10 @@
       <c r="B226" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="C226" s="3">
-        <v>0</v>
-      </c>
-      <c r="D226" s="4" t="s">
+      <c r="C226" s="4">
+        <v>0</v>
+      </c>
+      <c r="D226" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5270,10 +5283,10 @@
       <c r="B227" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="C227" s="3">
-        <v>0</v>
-      </c>
-      <c r="D227" s="4" t="s">
+      <c r="C227" s="4">
+        <v>0</v>
+      </c>
+      <c r="D227" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5284,10 +5297,10 @@
       <c r="B228" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="C228" s="3">
-        <v>0</v>
-      </c>
-      <c r="D228" s="4" t="s">
+      <c r="C228" s="4">
+        <v>0</v>
+      </c>
+      <c r="D228" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5298,10 +5311,10 @@
       <c r="B229" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="C229" s="3">
-        <v>0</v>
-      </c>
-      <c r="D229" s="4" t="s">
+      <c r="C229" s="4">
+        <v>0</v>
+      </c>
+      <c r="D229" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5312,10 +5325,10 @@
       <c r="B230" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="C230" s="3">
-        <v>0</v>
-      </c>
-      <c r="D230" s="4" t="s">
+      <c r="C230" s="4">
+        <v>0</v>
+      </c>
+      <c r="D230" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5326,10 +5339,10 @@
       <c r="B231" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="C231" s="3">
-        <v>0</v>
-      </c>
-      <c r="D231" s="4" t="s">
+      <c r="C231" s="4">
+        <v>0</v>
+      </c>
+      <c r="D231" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5340,10 +5353,10 @@
       <c r="B232" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="C232" s="3">
-        <v>0</v>
-      </c>
-      <c r="D232" s="4" t="s">
+      <c r="C232" s="4">
+        <v>0</v>
+      </c>
+      <c r="D232" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5354,10 +5367,10 @@
       <c r="B233" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="C233" s="3">
-        <v>0</v>
-      </c>
-      <c r="D233" s="4" t="s">
+      <c r="C233" s="4">
+        <v>0</v>
+      </c>
+      <c r="D233" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5368,10 +5381,10 @@
       <c r="B234" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="C234" s="3">
-        <v>0</v>
-      </c>
-      <c r="D234" s="4" t="s">
+      <c r="C234" s="4">
+        <v>0</v>
+      </c>
+      <c r="D234" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5382,10 +5395,10 @@
       <c r="B235" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="C235" s="3">
-        <v>0</v>
-      </c>
-      <c r="D235" s="4" t="s">
+      <c r="C235" s="4">
+        <v>0</v>
+      </c>
+      <c r="D235" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5396,10 +5409,10 @@
       <c r="B236" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="C236" s="3">
-        <v>0</v>
-      </c>
-      <c r="D236" s="4" t="s">
+      <c r="C236" s="4">
+        <v>0</v>
+      </c>
+      <c r="D236" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5410,10 +5423,10 @@
       <c r="B237" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="C237" s="3">
-        <v>0</v>
-      </c>
-      <c r="D237" s="4" t="s">
+      <c r="C237" s="4">
+        <v>0</v>
+      </c>
+      <c r="D237" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5424,10 +5437,10 @@
       <c r="B238" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="C238" s="3">
-        <v>0</v>
-      </c>
-      <c r="D238" s="4" t="s">
+      <c r="C238" s="4">
+        <v>0</v>
+      </c>
+      <c r="D238" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5438,10 +5451,10 @@
       <c r="B239" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="C239" s="3">
-        <v>0</v>
-      </c>
-      <c r="D239" s="4" t="s">
+      <c r="C239" s="4">
+        <v>0</v>
+      </c>
+      <c r="D239" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5452,10 +5465,10 @@
       <c r="B240" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="C240" s="3">
-        <v>0</v>
-      </c>
-      <c r="D240" s="4" t="s">
+      <c r="C240" s="4">
+        <v>0</v>
+      </c>
+      <c r="D240" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5466,10 +5479,10 @@
       <c r="B241" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="C241" s="3">
-        <v>0</v>
-      </c>
-      <c r="D241" s="4" t="s">
+      <c r="C241" s="4">
+        <v>0</v>
+      </c>
+      <c r="D241" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5480,10 +5493,10 @@
       <c r="B242" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="C242" s="3">
-        <v>0</v>
-      </c>
-      <c r="D242" s="4" t="s">
+      <c r="C242" s="4">
+        <v>0</v>
+      </c>
+      <c r="D242" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5494,10 +5507,10 @@
       <c r="B243" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="C243" s="3">
-        <v>0</v>
-      </c>
-      <c r="D243" s="4" t="s">
+      <c r="C243" s="4">
+        <v>0</v>
+      </c>
+      <c r="D243" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5508,10 +5521,10 @@
       <c r="B244" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="C244" s="3">
-        <v>0</v>
-      </c>
-      <c r="D244" s="4" t="s">
+      <c r="C244" s="4">
+        <v>0</v>
+      </c>
+      <c r="D244" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5522,10 +5535,10 @@
       <c r="B245" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="C245" s="3">
-        <v>0</v>
-      </c>
-      <c r="D245" s="4" t="s">
+      <c r="C245" s="4">
+        <v>0</v>
+      </c>
+      <c r="D245" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5536,10 +5549,10 @@
       <c r="B246" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="C246" s="3">
-        <v>0</v>
-      </c>
-      <c r="D246" s="4" t="s">
+      <c r="C246" s="4">
+        <v>0</v>
+      </c>
+      <c r="D246" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5550,10 +5563,10 @@
       <c r="B247" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="C247" s="3">
-        <v>0</v>
-      </c>
-      <c r="D247" s="4" t="s">
+      <c r="C247" s="4">
+        <v>0</v>
+      </c>
+      <c r="D247" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5564,10 +5577,10 @@
       <c r="B248" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="C248" s="3">
-        <v>0</v>
-      </c>
-      <c r="D248" s="4" t="s">
+      <c r="C248" s="4">
+        <v>0</v>
+      </c>
+      <c r="D248" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5578,10 +5591,10 @@
       <c r="B249" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="C249" s="3">
-        <v>0</v>
-      </c>
-      <c r="D249" s="4" t="s">
+      <c r="C249" s="4">
+        <v>0</v>
+      </c>
+      <c r="D249" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5592,10 +5605,10 @@
       <c r="B250" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="C250" s="3">
-        <v>0</v>
-      </c>
-      <c r="D250" s="4" t="s">
+      <c r="C250" s="4">
+        <v>0</v>
+      </c>
+      <c r="D250" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5606,10 +5619,10 @@
       <c r="B251" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="C251" s="3">
-        <v>0</v>
-      </c>
-      <c r="D251" s="4" t="s">
+      <c r="C251" s="4">
+        <v>0</v>
+      </c>
+      <c r="D251" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5620,10 +5633,10 @@
       <c r="B252" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="C252" s="3">
-        <v>0</v>
-      </c>
-      <c r="D252" s="4" t="s">
+      <c r="C252" s="4">
+        <v>0</v>
+      </c>
+      <c r="D252" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5634,10 +5647,10 @@
       <c r="B253" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="C253" s="3">
-        <v>0</v>
-      </c>
-      <c r="D253" s="4" t="s">
+      <c r="C253" s="4">
+        <v>0</v>
+      </c>
+      <c r="D253" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5648,10 +5661,10 @@
       <c r="B254" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="C254" s="3">
-        <v>0</v>
-      </c>
-      <c r="D254" s="4" t="s">
+      <c r="C254" s="4">
+        <v>0</v>
+      </c>
+      <c r="D254" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5662,10 +5675,10 @@
       <c r="B255" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="C255" s="3">
-        <v>0</v>
-      </c>
-      <c r="D255" s="4" t="s">
+      <c r="C255" s="4">
+        <v>0</v>
+      </c>
+      <c r="D255" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5676,10 +5689,10 @@
       <c r="B256" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="C256" s="3">
-        <v>0</v>
-      </c>
-      <c r="D256" s="4" t="s">
+      <c r="C256" s="4">
+        <v>0</v>
+      </c>
+      <c r="D256" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5690,10 +5703,10 @@
       <c r="B257" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="C257" s="3">
-        <v>0</v>
-      </c>
-      <c r="D257" s="4" t="s">
+      <c r="C257" s="4">
+        <v>0</v>
+      </c>
+      <c r="D257" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5704,10 +5717,10 @@
       <c r="B258" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="C258" s="3">
-        <v>0</v>
-      </c>
-      <c r="D258" s="4" t="s">
+      <c r="C258" s="4">
+        <v>0</v>
+      </c>
+      <c r="D258" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5718,10 +5731,10 @@
       <c r="B259" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="C259" s="3">
-        <v>0</v>
-      </c>
-      <c r="D259" s="4" t="s">
+      <c r="C259" s="4">
+        <v>0</v>
+      </c>
+      <c r="D259" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5732,10 +5745,10 @@
       <c r="B260" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="C260" s="3">
-        <v>0</v>
-      </c>
-      <c r="D260" s="4" t="s">
+      <c r="C260" s="4">
+        <v>0</v>
+      </c>
+      <c r="D260" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5746,10 +5759,10 @@
       <c r="B261" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="C261" s="3">
-        <v>0</v>
-      </c>
-      <c r="D261" s="4" t="s">
+      <c r="C261" s="4">
+        <v>0</v>
+      </c>
+      <c r="D261" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5760,10 +5773,10 @@
       <c r="B262" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="C262" s="3">
-        <v>0</v>
-      </c>
-      <c r="D262" s="4" t="s">
+      <c r="C262" s="4">
+        <v>0</v>
+      </c>
+      <c r="D262" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5774,10 +5787,10 @@
       <c r="B263" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="C263" s="3">
-        <v>0</v>
-      </c>
-      <c r="D263" s="4" t="s">
+      <c r="C263" s="4">
+        <v>0</v>
+      </c>
+      <c r="D263" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5788,10 +5801,10 @@
       <c r="B264" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="C264" s="3">
-        <v>0</v>
-      </c>
-      <c r="D264" s="4" t="s">
+      <c r="C264" s="4">
+        <v>0</v>
+      </c>
+      <c r="D264" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5802,10 +5815,10 @@
       <c r="B265" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="C265" s="3">
-        <v>0</v>
-      </c>
-      <c r="D265" s="4" t="s">
+      <c r="C265" s="4">
+        <v>0</v>
+      </c>
+      <c r="D265" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5816,10 +5829,10 @@
       <c r="B266" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="C266" s="3">
-        <v>0</v>
-      </c>
-      <c r="D266" s="4" t="s">
+      <c r="C266" s="4">
+        <v>0</v>
+      </c>
+      <c r="D266" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5830,10 +5843,10 @@
       <c r="B267" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="C267" s="3">
-        <v>0</v>
-      </c>
-      <c r="D267" s="4" t="s">
+      <c r="C267" s="4">
+        <v>0</v>
+      </c>
+      <c r="D267" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5844,10 +5857,10 @@
       <c r="B268" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="C268" s="3">
-        <v>0</v>
-      </c>
-      <c r="D268" s="4" t="s">
+      <c r="C268" s="4">
+        <v>0</v>
+      </c>
+      <c r="D268" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5858,10 +5871,10 @@
       <c r="B269" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="C269" s="3">
-        <v>0</v>
-      </c>
-      <c r="D269" s="4" t="s">
+      <c r="C269" s="4">
+        <v>0</v>
+      </c>
+      <c r="D269" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5872,10 +5885,10 @@
       <c r="B270" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="C270" s="3">
-        <v>0</v>
-      </c>
-      <c r="D270" s="4" t="s">
+      <c r="C270" s="4">
+        <v>0</v>
+      </c>
+      <c r="D270" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5886,10 +5899,10 @@
       <c r="B271" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="C271" s="3">
-        <v>0</v>
-      </c>
-      <c r="D271" s="4" t="s">
+      <c r="C271" s="4">
+        <v>0</v>
+      </c>
+      <c r="D271" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5900,10 +5913,10 @@
       <c r="B272" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="C272" s="3">
-        <v>0</v>
-      </c>
-      <c r="D272" s="4" t="s">
+      <c r="C272" s="4">
+        <v>0</v>
+      </c>
+      <c r="D272" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5914,10 +5927,10 @@
       <c r="B273" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="C273" s="3">
-        <v>0</v>
-      </c>
-      <c r="D273" s="4" t="s">
+      <c r="C273" s="4">
+        <v>0</v>
+      </c>
+      <c r="D273" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5928,10 +5941,10 @@
       <c r="B274" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="C274" s="3">
-        <v>0</v>
-      </c>
-      <c r="D274" s="4" t="s">
+      <c r="C274" s="4">
+        <v>0</v>
+      </c>
+      <c r="D274" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5942,10 +5955,10 @@
       <c r="B275" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="C275" s="3">
-        <v>0</v>
-      </c>
-      <c r="D275" s="4" t="s">
+      <c r="C275" s="4">
+        <v>0</v>
+      </c>
+      <c r="D275" s="3" t="s">
         <v>1</v>
       </c>
     </row>
